--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260701.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>157,755</t>
+          <t>156,755</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.23%</t>
+          <t>26.35%</t>
         </is>
       </c>
     </row>
@@ -633,56 +633,56 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>18,055</t>
+          <t>17,935</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.33%</t>
+          <t>9.28%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>58,375</t>
+          <t>113,700</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.65%</t>
+          <t>7.39%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>114,440</t>
+          <t>57,995</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.38%</t>
+          <t>7.20%</t>
         </is>
       </c>
     </row>
@@ -699,78 +699,78 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>138,965</t>
+          <t>138,065</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.44%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>74,965</t>
+          <t>67,610</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>6,565</t>
+          <t>74,475</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>68,050</t>
+          <t>6,525</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>51,705</t>
+          <t>51,365</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,625</t>
+          <t>22,475</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,933</t>
+          <t>20,793</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -853,78 +853,78 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>36,090</t>
+          <t>35,860</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>9,190</t>
+          <t>23,115</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>23,265</t>
+          <t>58,065</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>58,445</t>
+          <t>9,090</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -941,51 +941,51 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>88,125</t>
+          <t>87,555</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>13,451</t>
+          <t>3,701,902</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>22,330</t>
+          <t>30,228</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,22 +997,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>30,428</t>
+          <t>22,180</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>41,480</t>
+          <t>41,210</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1051,144 +1051,144 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>68,038</t>
+          <t>67,598</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>11,066</t>
+          <t>13,351</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>24,438</t>
+          <t>95,286,823</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>83,936,823</t>
+          <t>10,966</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,195</t>
+          <t>24,278</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>145,255</t>
+          <t>21,045</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>22,597</t>
+          <t>144,355</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1205,100 +1205,100 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,301</t>
+          <t>18,201</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,505</t>
+          <t>22,447</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,960</t>
+          <t>13,405</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>49,490</t>
+          <t>42,760</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,049,661</t>
+          <t>49,190</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>63,686,000</t>
+          <t>111,499,250</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,642,358</t>
+          <t>1,437,121</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
